--- a/K-mean練習題/練習題2.使用Excel計算分群-20筆.xlsx
+++ b/K-mean練習題/練習題2.使用Excel計算分群-20筆.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\K-mean練習題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\Data Mining MarkDown\K-mean練習題\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,7 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="題目" sheetId="1" r:id="rId1"/>
-    <sheet name="步驟1先計算形心" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>樣本</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -45,24 +44,6 @@
   <si>
     <t>原始聚類</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Income</t>
-  </si>
-  <si>
-    <t>聚類中心(第一次)</t>
-  </si>
-  <si>
-    <t>聚類1</t>
-  </si>
-  <si>
-    <t>聚類2</t>
-  </si>
-  <si>
-    <t>聚類3</t>
   </si>
 </sst>
 </file>
@@ -417,11 +398,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -727,11 +708,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="2"/>
       <c r="E1" s="10"/>
       <c r="F1" s="11"/>
@@ -1035,7 +1016,7 @@
       <c r="C17" s="4">
         <v>17</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <v>2</v>
       </c>
       <c r="E17" s="2"/>
@@ -1180,398 +1161,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
-  <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="19" max="20" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="22.2">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="2"/>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="22.2">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="T2" t="s">
-        <v>8</v>
-      </c>
-      <c r="U2" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="22.2">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4">
-        <v>5</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="S3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3">
-        <f>AVERAGE(B3:B7)</f>
-        <v>52.8</v>
-      </c>
-      <c r="U3">
-        <f>AVERAGE(B8:B17)</f>
-        <v>46.1</v>
-      </c>
-      <c r="V3">
-        <f>AVERAGE((B18:B22))</f>
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="22.2">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4">
-        <v>14</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="S4" t="s">
-        <v>6</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(C3:C7)</f>
-        <v>6</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(C8:C17)</f>
-        <v>11.2</v>
-      </c>
-      <c r="V4">
-        <f>AVERAGE(C18:C22)</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="22.2">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>71</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="22.2">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="22.2">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4">
-        <v>63</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="22.2">
-      <c r="A8" s="5">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4">
-        <v>49</v>
-      </c>
-      <c r="C8" s="4">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="22.2">
-      <c r="A9" s="5">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4">
-        <v>22</v>
-      </c>
-      <c r="C9" s="4">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="22.2">
-      <c r="A10" s="5">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="22.2">
-      <c r="A11" s="5">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>38</v>
-      </c>
-      <c r="C11" s="4">
-        <v>10</v>
-      </c>
-      <c r="D11" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="22.2">
-      <c r="A12" s="5">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4">
-        <v>10</v>
-      </c>
-      <c r="D12" s="8">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:22" ht="22.2">
-      <c r="A13" s="5">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>55</v>
-      </c>
-      <c r="C13" s="4">
-        <v>18</v>
-      </c>
-      <c r="D13" s="8">
-        <v>2</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:22" ht="22.2">
-      <c r="A14" s="5">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4">
-        <v>43</v>
-      </c>
-      <c r="C14" s="4">
-        <v>8</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:22" ht="22.2">
-      <c r="A15" s="5">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4">
-        <v>43</v>
-      </c>
-      <c r="C15" s="4">
-        <v>11</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2</v>
-      </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:22" ht="22.2">
-      <c r="A16" s="5">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4">
-        <v>57</v>
-      </c>
-      <c r="C16" s="4">
-        <v>14</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="22.2">
-      <c r="A17" s="5">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4">
-        <v>49</v>
-      </c>
-      <c r="C17" s="4">
-        <v>17</v>
-      </c>
-      <c r="D17" s="20">
-        <v>2</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="22.2">
-      <c r="A18" s="5">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4">
-        <v>35</v>
-      </c>
-      <c r="C18" s="4">
-        <v>8</v>
-      </c>
-      <c r="D18" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="22.2">
-      <c r="A19" s="5">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4">
-        <v>44</v>
-      </c>
-      <c r="C19" s="4">
-        <v>10</v>
-      </c>
-      <c r="D19" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="22.2">
-      <c r="A20" s="5">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4">
-        <v>28</v>
-      </c>
-      <c r="C20" s="4">
-        <v>10</v>
-      </c>
-      <c r="D20" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="22.2">
-      <c r="A21" s="5">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4">
-        <v>41</v>
-      </c>
-      <c r="C21" s="4">
-        <v>8</v>
-      </c>
-      <c r="D21" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="22.2">
-      <c r="A22" s="5">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4">
-        <v>45</v>
-      </c>
-      <c r="C22" s="4">
-        <v>10</v>
-      </c>
-      <c r="D22" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="22.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" ht="22.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="22.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>